--- a/results/Int All Data -0.3/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.3/Linea_fi_all.xlsx
@@ -2041,7 +2041,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.01172937085045842 +/- 0.0023804224450307975</t>
+          <t>0.011792601960164396 +/- 0.0023448854430336576</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-0.001043313310148608 +/- 0.0005299732726601412</t>
+          <t>-0.0010116977552956153 +/- 0.00046465186394874464</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>0.07780588049320267 +/- 0.004698820292907685</t>
+          <t>0.07783749604805565 +/- 0.004658978696121069</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.025658682634730513 +/- 0.003309839276417063</t>
+          <t>0.02562874251497004 +/- 0.0033129523817061234</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0012874251497005718 +/- 0.0009184348293519663</t>
+          <t>0.001317365269461046 +/- 0.0009001973879265171</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.001526489075127213 +/- 0.0010578028762090778</t>
+          <t>0.0014965579167913856 +/- 0.0010281690534162248</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -5226,72 +5226,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>0.00034998409163224944 +/- 0.0006275241146457752</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-0.011581291759465439 +/- 0.0014313995391921014</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-0.007795100222717089 +/- 0.0013137653720689004</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.00168628698695521 +/- 0.0009550321997966114</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.0004136175628380978 +/- 0.0006681514476614703</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.004390709513204005 +/- 0.0029907731466751347</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.021253579382755385 +/- 0.0023673019710770946</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.008749602290805014 +/- 0.0035749610331282547</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.10824053452115816 +/- 0.005458772765197381</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>-0.0007954183900731437 +/- 0.0007149922066256533</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>-0.0018453706649697254 +/- 0.0015959193387189853</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-0.0054724785237034055 +/- 0.0018486591213915352</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.009417753738466383 +/- 0.0015599937221929879</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.0003818008272351792 +/- 0.0006169493932442231</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.011581291759465439 +/- 0.0014313995391921014</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-0.007795100222717089 +/- 0.0013137653720689004</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.00168628698695521 +/- 0.0009550321997966114</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0.0004136175628380978 +/- 0.0006681514476614703</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.004390709513204005 +/- 0.0029907731466751347</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0.021253579382755385 +/- 0.0023673019710770946</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>0.008749602290805014 +/- 0.0035749610331282547</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0.10824053452115816 +/- 0.005458772765197381</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>-0.0007954183900731437 +/- 0.0007149922066256533</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>-0.0018453706649697254 +/- 0.0015959193387189853</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-0.0054724785237034055 +/- 0.0018486591213915352</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.009417753738466383 +/- 0.0015599937221929879</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.00034998409163224944 +/- 0.0006275241146457752</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.044032921810699545 +/- 0.0034341570752658567</t>
+          <t>0.044064577397910684 +/- 0.0034613325565904718</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.03339664450775559 +/- 0.004443637198753852</t>
+          <t>0.033364988920544444 +/- 0.004398190423034726</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.002722380500158261 +/- 0.0025371908717333335</t>
+          <t>0.0027540360873694048 +/- 0.0025247191366369777</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.023639455782312913 +/- 0.0046194683867543575</t>
+          <t>-0.023605442176870738 +/- 0.004589190469530057</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.007803934214769414 +/- 0.0015718874694555243</t>
+          <t>-0.007771686552724921 +/- 0.0014949147999354306</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -8326,74 +8326,74 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>-0.0007369432874079207 +/- 0.0013822271457945045</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.004261454661967268 +/- 0.001852014869159669</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.0010893944248637766 +/- 0.0005767382249279183</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-0.000448574174943972 +/- 0.00032675549590472806</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-6.4082024991996e-05 +/- 0.000128164049983992</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.02922140339634729 +/- 0.0012880327614381215</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.0018263377122717638 +/- 0.003139528762642463</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0.008971483498878519 +/- 0.003145898803879148</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0.1351810317206023 +/- 0.0025449924309273483</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-0.0002563280999679951 +/- 0.0003139365258293186</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0.02188401153476447 +/- 0.003533384304712241</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.0140660044857417 +/- 0.002028730037587537</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.000512656199935968 +/- 0.0006901845315135593</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.0007689842999039187 +/- 0.0013981047247210317</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.004261454661967268 +/- 0.001852014869159669</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>0.0010893944248637766 +/- 0.0005767382249279183</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.000448574174943972 +/- 0.00032675549590472806</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-6.4082024991996e-05 +/- 0.000128164049983992</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0.02922140339634729 +/- 0.0012880327614381215</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.0018263377122717638 +/- 0.003139528762642463</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0.008971483498878519 +/- 0.003145898803879148</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0.1351810317206023 +/- 0.0025449924309273483</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.0002563280999679951 +/- 0.0003139365258293186</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>0.02188401153476447 +/- 0.003533384304712241</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0.0140660044857417 +/- 0.002028730037587537</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.000512656199935968 +/- 0.0006901845315135593</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.0007369432874079207 +/- 0.0013822271457945045</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>0.006344120474206938 +/- 0.0016325202438778638</t>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>6.408202499192938e-05 +/- 0.0011711417419094407</t>
+          <t>-6.661338147750939e-17 +/- 0.001137343117545564</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>0.017750720922781116 +/- 0.0034455636164742232</t>
+          <t>0.01771867991028512 +/- 0.003403141686857956</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
